--- a/testakten/rentenrecht-betriebsrente-pensionskasse-kuerzung-wiesbaden/unterlagen_bav_checkliste.xlsx
+++ b/testakten/rentenrecht-betriebsrente-pensionskasse-kuerzung-wiesbaden/unterlagen_bav_checkliste.xlsx
@@ -7,9 +7,18 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daten" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unterlagen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fristen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berechnung" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Unterlagen'!$A$1:$G$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Unterlagen'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fristen'!$A$1:$F$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Fristen'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Berechnung'!$A$1:$E$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Berechnung'!$1:$1</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +34,31 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00183941"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7EFF1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +66,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00C7D2D5"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -411,106 +446,662 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Unterlage</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Datum</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Absender</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Vorhanden</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Bedeutung</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Nachforderung</t>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Fundstelle</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Offene Frage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Anforderung bis</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Versorgungsordnung 1998</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Versorgungsordnung</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>15.06.1998</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Arbeitgeber</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Kopie</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>grüner Hefter Register 1</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>vollständige Anlagen und Änderungen</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>10.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Aufnahmebestätigung</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>01.10.1989</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Pensionskasse</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Personalakte</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Mitgliedsbeginn und Tarif</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>10.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Rentenbeginnberechnung</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>18.03.2020</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Pensionskasse</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>ja</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Zusagegrundlage</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>vollständige Anlage</t>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Register 2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Versorgungspunkte abgleichen</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>08.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Rentenmitteilung 2025</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>14.06.2025</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Pensionskasse</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Register 2</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Ausgangsbetrag</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>erledigt</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Kürzungsmitteilung</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>07.06.2026</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Pensionskasse</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Register 3</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Rentenfaktor und Tarif</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>erledigt</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Sanierungsbeschluss</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>26.02.2026</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Pensionskasse</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Auszug</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Register 3</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>vollständiger Beschluss und Satzungsgrundlage</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>12.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Arbeitgeberangebot</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>18.06.2026</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Arbeitgeber</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Register 4</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Abgeltungsreichweite</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>15.07.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Anpassungsentscheidung</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>unbekannt</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Arbeitgeber</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>nicht abgelegt</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Stichtag und Datengrundlage</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>12.07.2026</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G9"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Vorgang</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Datum</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Vorfrist</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Zuständig</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Notiz</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Angebotsfrist Arbeitgeber</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>15.07.2026</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>08.07.2026</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Jessen</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>keine Erklärung ohne Mandantenfreigabe</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Sanierungsplan Pensionskasse</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>nein</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Kürzungsgrund</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Kasse</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Einwendungen Kassenberechnung</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>31.08.2026</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>17.08.2026</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Jessen</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>notiert</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Rentenverlauf abwarten</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Anpassungsentscheidung Arbeitgeber</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>nein</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>BetrAVG</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Arbeitgeber</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>erste gekürzte Zahlung</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>31.08.2026</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>24.08.2026</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Özdemir</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Kontrolle</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Kontoauszug anfordern</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Monat EUR</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Jahr EUR</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Quelle</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Sicherheitsgrad</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Bisherige Kassenrente</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>486.70</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>5840.40</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Mitteilung 2025</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>belegt</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Neue Kassenrente</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>445.80</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>5349.60</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Mitteilung 2026</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>angekündigt</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Differenz</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>40.90</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>490.80</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Subtraktion</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>rechnerisch</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Arbeitgeberangebot</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>720.00</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Schreiben 18.06.2026</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>befristet</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToWidth="1"/>
 </worksheet>
 </file>